--- a/data/experiments_block_differences.xlsx
+++ b/data/experiments_block_differences.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marta\Nextcloud\Shared_SweetC\Experiments\ExpPrefer\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57934E4B-7B33-412C-A86E-D32B1272CB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D7B2FD-9D0A-4954-889A-FE26B0A28194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43890" yWindow="870" windowWidth="14400" windowHeight="8175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="heatmap_data-SIMON" sheetId="1" r:id="rId1"/>
@@ -25,36 +25,6 @@
     <t>Participant</t>
   </si>
   <si>
-    <t>1-10</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>4-5</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>7-8</t>
-  </si>
-  <si>
-    <t>8-9</t>
-  </si>
-  <si>
-    <t>9-10</t>
-  </si>
-  <si>
     <t>Experiment</t>
   </si>
   <si>
@@ -62,6 +32,36 @@
   </si>
   <si>
     <t>Stroop</t>
+  </si>
+  <si>
+    <t>10-1</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>5-4</t>
+  </si>
+  <si>
+    <t>6-5</t>
+  </si>
+  <si>
+    <t>7-6</t>
+  </si>
+  <si>
+    <t>8-7</t>
+  </si>
+  <si>
+    <t>9-8</t>
+  </si>
+  <si>
+    <t>10-9</t>
   </si>
 </sst>
 </file>
@@ -120,9 +120,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -436,38 +439,38 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -505,7 +508,7 @@
         <v>-4</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -543,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -581,7 +584,7 @@
         <v>16</v>
       </c>
       <c r="L4" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -619,7 +622,7 @@
         <v>11</v>
       </c>
       <c r="L5" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -657,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -695,7 +698,7 @@
         <v>-2</v>
       </c>
       <c r="L7" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -733,7 +736,7 @@
         <v>16</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -771,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -809,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -847,7 +850,7 @@
         <v>-1</v>
       </c>
       <c r="L11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -885,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -923,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="L13" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -961,7 +964,7 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -999,7 +1002,7 @@
         <v>11</v>
       </c>
       <c r="L15" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -1037,7 +1040,7 @@
         <v>-13</v>
       </c>
       <c r="L16" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -1075,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -1113,7 +1116,7 @@
         <v>14</v>
       </c>
       <c r="L18" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -1151,7 +1154,7 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
@@ -1189,7 +1192,7 @@
         <v>-11</v>
       </c>
       <c r="L20" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
@@ -1227,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="L21" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -1265,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
@@ -1303,7 +1306,7 @@
         <v>16</v>
       </c>
       <c r="L23" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
@@ -1341,7 +1344,7 @@
         <v>9</v>
       </c>
       <c r="L24" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
@@ -1379,7 +1382,7 @@
         <v>3</v>
       </c>
       <c r="L25" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
@@ -1417,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
@@ -1455,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
@@ -1493,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
@@ -1531,7 +1534,7 @@
         <v>8</v>
       </c>
       <c r="L29" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
@@ -1569,7 +1572,7 @@
         <v>-15</v>
       </c>
       <c r="L30" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
@@ -1607,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
@@ -1645,7 +1648,7 @@
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
@@ -1683,7 +1686,7 @@
         <v>11</v>
       </c>
       <c r="L33" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
@@ -1721,7 +1724,7 @@
         <v>2</v>
       </c>
       <c r="L34" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
@@ -1759,7 +1762,7 @@
         <v>3</v>
       </c>
       <c r="L35" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
@@ -1797,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -1835,7 +1838,7 @@
         <v>2</v>
       </c>
       <c r="L37" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
@@ -1873,7 +1876,7 @@
         <v>4</v>
       </c>
       <c r="L38" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
@@ -1911,7 +1914,7 @@
         <v>2</v>
       </c>
       <c r="L39" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
@@ -1949,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
@@ -1987,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
@@ -2025,7 +2028,7 @@
         <v>-1</v>
       </c>
       <c r="L42" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
@@ -2063,7 +2066,7 @@
         <v>16</v>
       </c>
       <c r="L43" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
@@ -2101,7 +2104,7 @@
         <v>2</v>
       </c>
       <c r="L44" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
@@ -2139,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="L45" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
@@ -2177,7 +2180,7 @@
         <v>8</v>
       </c>
       <c r="L46" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
@@ -2215,7 +2218,7 @@
         <v>4</v>
       </c>
       <c r="L47" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
@@ -2253,7 +2256,7 @@
         <v>11</v>
       </c>
       <c r="L48" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
@@ -2291,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
@@ -2329,7 +2332,7 @@
         <v>7</v>
       </c>
       <c r="L50" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
@@ -2367,7 +2370,7 @@
         <v>-15</v>
       </c>
       <c r="L51" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
@@ -2405,7 +2408,7 @@
         <v>-16</v>
       </c>
       <c r="L52" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
@@ -2443,7 +2446,7 @@
         <v>16</v>
       </c>
       <c r="L53" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
@@ -2481,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
@@ -2519,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
@@ -2557,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
@@ -2595,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
@@ -2633,7 +2636,7 @@
         <v>8</v>
       </c>
       <c r="L58" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
@@ -2671,7 +2674,7 @@
         <v>16</v>
       </c>
       <c r="L59" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
@@ -2709,7 +2712,7 @@
         <v>-4</v>
       </c>
       <c r="L60" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
@@ -2747,7 +2750,7 @@
         <v>-3</v>
       </c>
       <c r="L61" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
@@ -2785,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
@@ -2823,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
@@ -2861,7 +2864,7 @@
         <v>-9</v>
       </c>
       <c r="L64" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.35">
@@ -2899,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
@@ -2937,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.35">
@@ -2975,7 +2978,7 @@
         <v>12</v>
       </c>
       <c r="L67" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
@@ -3013,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="L68" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
@@ -3051,7 +3054,7 @@
         <v>-14</v>
       </c>
       <c r="L69" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
@@ -3089,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.35">
@@ -3127,7 +3130,7 @@
         <v>-4</v>
       </c>
       <c r="L71" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
@@ -3165,7 +3168,7 @@
         <v>7</v>
       </c>
       <c r="L72" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.35">
@@ -3203,7 +3206,7 @@
         <v>6</v>
       </c>
       <c r="L73" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
@@ -3241,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.35">
@@ -3279,7 +3282,7 @@
         <v>10</v>
       </c>
       <c r="L75" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
@@ -3317,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.35">
@@ -3355,7 +3358,7 @@
         <v>-4</v>
       </c>
       <c r="L77" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
@@ -3393,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="L78" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.35">
@@ -3431,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
@@ -3469,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.35">
@@ -3507,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
@@ -3545,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.35">
@@ -3583,7 +3586,7 @@
         <v>-4</v>
       </c>
       <c r="L83" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
@@ -3621,7 +3624,7 @@
         <v>8</v>
       </c>
       <c r="L84" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.35">
@@ -3659,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
@@ -3697,7 +3700,7 @@
         <v>2</v>
       </c>
       <c r="L86" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.35">
@@ -3735,7 +3738,7 @@
         <v>-16</v>
       </c>
       <c r="L87" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
@@ -3773,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.35">
@@ -3811,7 +3814,7 @@
         <v>8</v>
       </c>
       <c r="L89" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
@@ -3849,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.35">
@@ -3887,7 +3890,7 @@
         <v>8</v>
       </c>
       <c r="L91" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
@@ -3925,7 +3928,7 @@
         <v>7</v>
       </c>
       <c r="L92" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.35">
@@ -3963,7 +3966,7 @@
         <v>-7</v>
       </c>
       <c r="L93" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
@@ -4001,7 +4004,7 @@
         <v>16</v>
       </c>
       <c r="L94" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.35">
@@ -4039,7 +4042,7 @@
         <v>8</v>
       </c>
       <c r="L95" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
@@ -4077,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.35">
@@ -4115,7 +4118,7 @@
         <v>11</v>
       </c>
       <c r="L97" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
@@ -4153,7 +4156,7 @@
         <v>6</v>
       </c>
       <c r="L98" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.35">
@@ -4191,7 +4194,7 @@
         <v>-2</v>
       </c>
       <c r="L99" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
@@ -4229,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.35">
@@ -4267,7 +4270,7 @@
         <v>-1</v>
       </c>
       <c r="L101" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
@@ -4305,7 +4308,7 @@
         <v>2</v>
       </c>
       <c r="L102" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.35">
@@ -4343,7 +4346,7 @@
         <v>-21</v>
       </c>
       <c r="L103" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
@@ -4381,7 +4384,7 @@
         <v>15</v>
       </c>
       <c r="L104" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.35">
@@ -4419,7 +4422,7 @@
         <v>-23</v>
       </c>
       <c r="L105" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
@@ -4457,7 +4460,7 @@
         <v>-9</v>
       </c>
       <c r="L106" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.35">
@@ -4495,7 +4498,7 @@
         <v>-23</v>
       </c>
       <c r="L107" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
@@ -4533,7 +4536,7 @@
         <v>12</v>
       </c>
       <c r="L108" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.35">
@@ -4571,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
@@ -4609,7 +4612,7 @@
         <v>6</v>
       </c>
       <c r="L110" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.35">
@@ -4647,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
@@ -4685,7 +4688,7 @@
         <v>16</v>
       </c>
       <c r="L112" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.35">
@@ -4723,7 +4726,7 @@
         <v>25</v>
       </c>
       <c r="L113" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
@@ -4761,7 +4764,7 @@
         <v>-5</v>
       </c>
       <c r="L114" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.35">
@@ -4799,7 +4802,7 @@
         <v>9</v>
       </c>
       <c r="L115" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
@@ -4837,7 +4840,7 @@
         <v>1</v>
       </c>
       <c r="L116" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.35">
@@ -4875,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
@@ -4913,7 +4916,7 @@
         <v>10</v>
       </c>
       <c r="L118" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.35">
@@ -4951,7 +4954,7 @@
         <v>-30</v>
       </c>
       <c r="L119" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
@@ -4989,7 +4992,7 @@
         <v>-15</v>
       </c>
       <c r="L120" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.35">
@@ -5027,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="L121" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
@@ -5065,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.35">
@@ -5103,7 +5106,7 @@
         <v>3</v>
       </c>
       <c r="L123" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
@@ -5141,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.35">
@@ -5179,7 +5182,7 @@
         <v>-1</v>
       </c>
       <c r="L125" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
@@ -5217,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="L126" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.35">
@@ -5255,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.35">
@@ -5293,7 +5296,7 @@
         <v>12</v>
       </c>
       <c r="L128" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.35">
@@ -5331,7 +5334,7 @@
         <v>5</v>
       </c>
       <c r="L129" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.35">
@@ -5369,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="L130" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.35">
@@ -5407,7 +5410,7 @@
         <v>-1</v>
       </c>
       <c r="L131" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.35">
@@ -5445,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="L132" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.35">
@@ -5483,7 +5486,7 @@
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.35">
@@ -5521,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="L134" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.35">
@@ -5559,7 +5562,7 @@
         <v>-1</v>
       </c>
       <c r="L135" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.35">
@@ -5597,7 +5600,7 @@
         <v>3</v>
       </c>
       <c r="L136" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.35">
@@ -5635,7 +5638,7 @@
         <v>3</v>
       </c>
       <c r="L137" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.35">
@@ -5673,7 +5676,7 @@
         <v>1</v>
       </c>
       <c r="L138" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.35">
@@ -5711,7 +5714,7 @@
         <v>-8</v>
       </c>
       <c r="L139" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.35">
@@ -5749,7 +5752,7 @@
         <v>-14</v>
       </c>
       <c r="L140" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.35">
@@ -5787,7 +5790,7 @@
         <v>-6</v>
       </c>
       <c r="L141" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.35">
@@ -5825,7 +5828,7 @@
         <v>2</v>
       </c>
       <c r="L142" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.35">
@@ -5863,7 +5866,7 @@
         <v>-1</v>
       </c>
       <c r="L143" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.35">
@@ -5901,7 +5904,7 @@
         <v>-19</v>
       </c>
       <c r="L144" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.35">
@@ -5939,7 +5942,7 @@
         <v>-30</v>
       </c>
       <c r="L145" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.35">
@@ -5977,7 +5980,7 @@
         <v>-29</v>
       </c>
       <c r="L146" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.35">
@@ -6015,7 +6018,7 @@
         <v>-11</v>
       </c>
       <c r="L147" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.35">
@@ -6053,7 +6056,7 @@
         <v>5</v>
       </c>
       <c r="L148" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.35">
@@ -6091,7 +6094,7 @@
         <v>-15</v>
       </c>
       <c r="L149" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.35">
@@ -6129,7 +6132,7 @@
         <v>-8</v>
       </c>
       <c r="L150" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.35">
@@ -6167,7 +6170,7 @@
         <v>6</v>
       </c>
       <c r="L151" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.35">
@@ -6205,7 +6208,7 @@
         <v>-21</v>
       </c>
       <c r="L152" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.35">
@@ -6243,7 +6246,7 @@
         <v>-2</v>
       </c>
       <c r="L153" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.35">
@@ -6281,7 +6284,7 @@
         <v>-14</v>
       </c>
       <c r="L154" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.35">
@@ -6319,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="L155" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.35">
@@ -6357,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="L156" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.35">
@@ -6395,7 +6398,7 @@
         <v>5</v>
       </c>
       <c r="L157" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.35">
@@ -6433,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="L158" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.35">
@@ -6471,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="L159" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.35">
@@ -6509,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="L160" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.35">
@@ -6547,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="L161" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.35">
@@ -6585,7 +6588,7 @@
         <v>15</v>
       </c>
       <c r="L162" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.35">
@@ -6623,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="L163" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.35">
@@ -6661,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="L164" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.35">
@@ -6699,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="L165" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.35">
@@ -6737,7 +6740,7 @@
         <v>15</v>
       </c>
       <c r="L166" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.35">
@@ -6775,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="L167" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.35">
@@ -6813,7 +6816,7 @@
         <v>1</v>
       </c>
       <c r="L168" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.35">
@@ -6851,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="L169" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.35">
@@ -6889,7 +6892,7 @@
         <v>0</v>
       </c>
       <c r="L170" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.35">
@@ -6927,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="L171" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.35">
@@ -6965,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="L172" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.35">
@@ -7003,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="L173" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.35">
@@ -7041,7 +7044,7 @@
         <v>13</v>
       </c>
       <c r="L174" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.35">
@@ -7079,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="L175" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.35">
@@ -7117,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="L176" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.35">
@@ -7155,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="L177" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.35">
@@ -7193,7 +7196,7 @@
         <v>15</v>
       </c>
       <c r="L178" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.35">
@@ -7231,7 +7234,7 @@
         <v>22</v>
       </c>
       <c r="L179" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.35">
@@ -7269,7 +7272,7 @@
         <v>1</v>
       </c>
       <c r="L180" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.35">
@@ -7307,7 +7310,7 @@
         <v>14</v>
       </c>
       <c r="L181" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.35">
@@ -7345,7 +7348,7 @@
         <v>7</v>
       </c>
       <c r="L182" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.35">
@@ -7383,7 +7386,7 @@
         <v>6</v>
       </c>
       <c r="L183" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.35">
@@ -7421,7 +7424,7 @@
         <v>11</v>
       </c>
       <c r="L184" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.35">
@@ -7459,7 +7462,7 @@
         <v>-1</v>
       </c>
       <c r="L185" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.35">
@@ -7497,7 +7500,7 @@
         <v>19</v>
       </c>
       <c r="L186" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.35">
@@ -7535,7 +7538,7 @@
         <v>2</v>
       </c>
       <c r="L187" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.35">
@@ -7573,7 +7576,7 @@
         <v>2</v>
       </c>
       <c r="L188" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.35">
@@ -7611,7 +7614,7 @@
         <v>-11</v>
       </c>
       <c r="L189" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.35">
@@ -7649,7 +7652,7 @@
         <v>2</v>
       </c>
       <c r="L190" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.35">
@@ -7687,7 +7690,7 @@
         <v>16</v>
       </c>
       <c r="L191" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.35">
@@ -7725,7 +7728,7 @@
         <v>-8</v>
       </c>
       <c r="L192" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.35">
@@ -7763,7 +7766,7 @@
         <v>7</v>
       </c>
       <c r="L193" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.35">
@@ -7801,7 +7804,7 @@
         <v>-2</v>
       </c>
       <c r="L194" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.35">
@@ -7839,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="L195" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.35">
@@ -7877,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="L196" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.35">
@@ -7915,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="L197" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.35">
@@ -7953,7 +7956,7 @@
         <v>15</v>
       </c>
       <c r="L198" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.35">
@@ -7991,7 +7994,7 @@
         <v>-4</v>
       </c>
       <c r="L199" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.35">
@@ -8029,7 +8032,7 @@
         <v>-2</v>
       </c>
       <c r="L200" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.35">
@@ -8067,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="L201" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
